--- a/gui_key.xlsx
+++ b/gui_key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/danli_ad_unc_edu/Documents/github/CALFEWS_waterFutures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0bab411f96558118/Documents/GitHub/CALFEWSv2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABA9E07-7A52-4439-B1A2-0C6EEF77A11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{0ABA9E07-7A52-4439-B1A2-0C6EEF77A11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A21D278F-2137-4A52-B66C-C772A09A913C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="783" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="783" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="input_data" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="683">
   <si>
     <t>Object List</t>
   </si>
@@ -561,21 +561,6 @@
     <t>metropolitan</t>
   </si>
   <si>
-    <t>Metropolitan Water District</t>
-  </si>
-  <si>
-    <t>castaic</t>
-  </si>
-  <si>
-    <t>Castaic Water District</t>
-  </si>
-  <si>
-    <t>coachella</t>
-  </si>
-  <si>
-    <t>Coachella Water District</t>
-  </si>
-  <si>
     <t>pioneer</t>
   </si>
   <si>
@@ -822,12 +807,6 @@
     <t>MET</t>
   </si>
   <si>
-    <t>CCH</t>
-  </si>
-  <si>
-    <t>CTL</t>
-  </si>
-  <si>
     <t>Distance from the Golden Gate Bridge to the X2 line of 2ppm salinity in the delta</t>
   </si>
   <si>
@@ -1804,6 +1783,309 @@
   </si>
   <si>
     <t xml:space="preserve">Pumping through Jones/Tracy pumping plant (CVP) </t>
+  </si>
+  <si>
+    <t>dummy</t>
+  </si>
+  <si>
+    <t>dummy2</t>
+  </si>
+  <si>
+    <t>DUMMY</t>
+  </si>
+  <si>
+    <t>DUMMY2</t>
+  </si>
+  <si>
+    <t>Los Angeles Aqueduct Feeder</t>
+  </si>
+  <si>
+    <t>California Aqueduct Feeder</t>
+  </si>
+  <si>
+    <t>coloradocompact</t>
+  </si>
+  <si>
+    <t>CMPT</t>
+  </si>
+  <si>
+    <t>owensvalley</t>
+  </si>
+  <si>
+    <t>OVY</t>
+  </si>
+  <si>
+    <t>Colorado River Rights for MET</t>
+  </si>
+  <si>
+    <t>LA Aquduct Right for LADWP (MET)</t>
+  </si>
+  <si>
+    <t>preferential</t>
+  </si>
+  <si>
+    <t>PRF</t>
+  </si>
+  <si>
+    <t>Internal MET Distribution (Future)</t>
+  </si>
+  <si>
+    <t>antelopekern</t>
+  </si>
+  <si>
+    <t>AVEK</t>
+  </si>
+  <si>
+    <t>SWP Southern</t>
+  </si>
+  <si>
+    <t>crestline</t>
+  </si>
+  <si>
+    <t>desert</t>
+  </si>
+  <si>
+    <t>mojavewater</t>
+  </si>
+  <si>
+    <t>palmdale</t>
+  </si>
+  <si>
+    <t>sangabriel</t>
+  </si>
+  <si>
+    <t>santaclarita</t>
+  </si>
+  <si>
+    <t>ventura</t>
+  </si>
+  <si>
+    <t>coachellavalley</t>
+  </si>
+  <si>
+    <t>sanbernadino</t>
+  </si>
+  <si>
+    <t>sangorgonio</t>
+  </si>
+  <si>
+    <t>CRL</t>
+  </si>
+  <si>
+    <t>DST</t>
+  </si>
+  <si>
+    <t>MJV</t>
+  </si>
+  <si>
+    <t>SNA</t>
+  </si>
+  <si>
+    <t>PMD</t>
+  </si>
+  <si>
+    <t>SGO</t>
+  </si>
+  <si>
+    <t>SGL</t>
+  </si>
+  <si>
+    <t>SCL</t>
+  </si>
+  <si>
+    <t>VTA</t>
+  </si>
+  <si>
+    <t>CCHV</t>
+  </si>
+  <si>
+    <t>SBN</t>
+  </si>
+  <si>
+    <t>Urban (LA/SD)</t>
+  </si>
+  <si>
+    <t>anaheim</t>
+  </si>
+  <si>
+    <t>beverlyhills</t>
+  </si>
+  <si>
+    <t>burbank</t>
+  </si>
+  <si>
+    <t>compton</t>
+  </si>
+  <si>
+    <t>fullerton</t>
+  </si>
+  <si>
+    <t>glendale</t>
+  </si>
+  <si>
+    <t>longbeach</t>
+  </si>
+  <si>
+    <t>losangeles</t>
+  </si>
+  <si>
+    <t>pasadena</t>
+  </si>
+  <si>
+    <t>sanfernando</t>
+  </si>
+  <si>
+    <t>sanmarino</t>
+  </si>
+  <si>
+    <t>santaaana</t>
+  </si>
+  <si>
+    <t>santamonica</t>
+  </si>
+  <si>
+    <t>torrance</t>
+  </si>
+  <si>
+    <t>calleguas</t>
+  </si>
+  <si>
+    <t>centralbasin</t>
+  </si>
+  <si>
+    <t>eastern</t>
+  </si>
+  <si>
+    <t>foothill</t>
+  </si>
+  <si>
+    <t>inlandempire</t>
+  </si>
+  <si>
+    <t>lasvirgenes</t>
+  </si>
+  <si>
+    <t>orangecounty</t>
+  </si>
+  <si>
+    <t>sandiegocounty</t>
+  </si>
+  <si>
+    <t>threevalleys</t>
+  </si>
+  <si>
+    <t>westbasin</t>
+  </si>
+  <si>
+    <t>riversidecounty</t>
+  </si>
+  <si>
+    <t>uppersangabriel</t>
+  </si>
+  <si>
+    <t>ANA</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>COM</t>
+  </si>
+  <si>
+    <t>FUL</t>
+  </si>
+  <si>
+    <t>PAS</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>EAS</t>
+  </si>
+  <si>
+    <t>ORA</t>
+  </si>
+  <si>
+    <t>BVH</t>
+  </si>
+  <si>
+    <t>GLN</t>
+  </si>
+  <si>
+    <t>FOT</t>
+  </si>
+  <si>
+    <t>LAV</t>
+  </si>
+  <si>
+    <t>LNB</t>
+  </si>
+  <si>
+    <t>LAX</t>
+  </si>
+  <si>
+    <t>SFN</t>
+  </si>
+  <si>
+    <t>SMO</t>
+  </si>
+  <si>
+    <t>SNM</t>
+  </si>
+  <si>
+    <t>CLG</t>
+  </si>
+  <si>
+    <t>CBN</t>
+  </si>
+  <si>
+    <t>INE</t>
+  </si>
+  <si>
+    <t>SDC</t>
+  </si>
+  <si>
+    <t>3VY</t>
+  </si>
+  <si>
+    <t>WBN</t>
+  </si>
+  <si>
+    <t>RSC</t>
+  </si>
+  <si>
+    <t>USG</t>
+  </si>
+  <si>
+    <t>Urban (MET internal)</t>
+  </si>
+  <si>
+    <t>westside</t>
+  </si>
+  <si>
+    <t>eastside</t>
+  </si>
+  <si>
+    <t>amargosa</t>
+  </si>
+  <si>
+    <t>highdesert</t>
+  </si>
+  <si>
+    <t>WSD</t>
+  </si>
+  <si>
+    <t>ESD</t>
+  </si>
+  <si>
+    <t>UAG</t>
+  </si>
+  <si>
+    <t>HDT</t>
+  </si>
+  <si>
+    <t>AVEK WB</t>
   </si>
 </sst>
 </file>
@@ -1940,7 +2222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1953,6 +2235,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2234,610 +2518,610 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="36.1796875" customWidth="1"/>
-    <col min="2" max="2" width="46.08984375" customWidth="1"/>
-    <col min="4" max="4" width="17.81640625" customWidth="1"/>
+    <col min="1" max="1" width="36.1328125" customWidth="1"/>
+    <col min="2" max="2" width="46.1328125" customWidth="1"/>
+    <col min="4" max="4" width="17.86328125" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="6" max="6" width="17.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="B2" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="D2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F2" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C3">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C4">
         <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B6" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C6">
         <v>12</v>
       </c>
       <c r="D6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F6" t="s">
         <v>325</v>
       </c>
-      <c r="E6" t="s">
-        <v>331</v>
-      </c>
-      <c r="F6" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E7" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B8" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E8" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="F8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B9" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C9">
         <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E9" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F9" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B10" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C10">
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E10" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F10" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B11" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C11">
         <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E11" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F11" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B12" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C12">
         <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E12" t="s">
+        <v>519</v>
+      </c>
+      <c r="F12" t="s">
         <v>526</v>
       </c>
-      <c r="F12" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="B13" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C13">
         <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E13" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F13" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B14" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C14">
         <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E14" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F14" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B15" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C15">
         <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E15" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F15" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="B16" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C16">
         <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E16" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F16" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B17" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C17">
         <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E17" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F17" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="B18" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C18">
         <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E18" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F18" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B19" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C19">
         <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E19" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F19" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="B20" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C20">
         <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E20" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F20" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="B21" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C21">
         <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E21" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F21" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B22" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C22">
         <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E22" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F22" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B23" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C23">
         <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E23" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F23" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B24" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C24">
         <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E24" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F24" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="B25" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C25">
         <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E25" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F25" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="B26" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C26">
         <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E26" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F26" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B27" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C27">
         <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E27" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F27" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="B28" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C28">
         <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E28" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F28" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="B29" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C29">
         <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E29" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F29" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="B30" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C30">
         <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E30" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F30" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -2850,15 +3134,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.59765625" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="20.08984375" customWidth="1"/>
-    <col min="5" max="5" width="38.1796875" customWidth="1"/>
+    <col min="3" max="3" width="20.1328125" customWidth="1"/>
+    <col min="5" max="5" width="38.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2869,51 +3153,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" t="s">
-        <v>260</v>
-      </c>
-      <c r="C4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2929,39 +3180,39 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28.36328125" customWidth="1"/>
-    <col min="2" max="2" width="49.453125" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.08984375" customWidth="1"/>
-    <col min="7" max="7" width="38.1796875" customWidth="1"/>
+    <col min="1" max="1" width="28.3984375" customWidth="1"/>
+    <col min="2" max="2" width="49.3984375" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" customWidth="1"/>
+    <col min="4" max="4" width="6.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1328125" customWidth="1"/>
+    <col min="7" max="7" width="38.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -2970,15 +3221,15 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -2990,12 +3241,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -3007,12 +3258,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="B5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -3021,15 +3272,15 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -3038,15 +3289,15 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -3055,15 +3306,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -3072,15 +3323,15 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="B9" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -3089,15 +3340,15 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B10" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -3106,15 +3357,15 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="B11" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -3123,15 +3374,15 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B12" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -3140,15 +3391,15 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B13" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -3157,15 +3408,15 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B14" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -3174,15 +3425,15 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B15" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -3191,15 +3442,15 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B16" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -3208,15 +3459,15 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B17" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -3225,15 +3476,15 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="B18" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
@@ -3242,15 +3493,15 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B19" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
@@ -3259,15 +3510,15 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B20" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -3276,15 +3527,15 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="B21" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
@@ -3293,15 +3544,15 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B22" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
@@ -3310,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3320,16 +3571,16 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.36328125" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" customWidth="1"/>
-    <col min="4" max="4" width="10.6328125" customWidth="1"/>
+    <col min="1" max="1" width="14.3984375" customWidth="1"/>
+    <col min="2" max="2" width="18.3984375" customWidth="1"/>
+    <col min="3" max="3" width="17.86328125" customWidth="1"/>
+    <col min="4" max="4" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3340,147 +3591,191 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="B2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>464</v>
-      </c>
-      <c r="B5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>461</v>
-      </c>
-      <c r="B6" t="s">
-        <v>462</v>
-      </c>
-      <c r="C6" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B10" t="s">
+        <v>449</v>
+      </c>
+      <c r="C10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B11" t="s">
         <v>452</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C11" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>179</v>
-      </c>
-      <c r="B9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C9" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>455</v>
-      </c>
-      <c r="B10" t="s">
-        <v>456</v>
-      </c>
-      <c r="C10" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>458</v>
-      </c>
-      <c r="B11" t="s">
-        <v>459</v>
-      </c>
-      <c r="C11" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" t="s">
-        <v>451</v>
-      </c>
       <c r="C12" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B13" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C13" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B14" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C14" t="s">
-        <v>584</v>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>674</v>
+      </c>
+      <c r="B15" t="s">
+        <v>678</v>
+      </c>
+      <c r="C15" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>675</v>
+      </c>
+      <c r="B16" t="s">
+        <v>679</v>
+      </c>
+      <c r="C16" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>676</v>
+      </c>
+      <c r="B17" t="s">
+        <v>680</v>
+      </c>
+      <c r="C17" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>677</v>
+      </c>
+      <c r="B18" t="s">
+        <v>681</v>
+      </c>
+      <c r="C18" t="s">
+        <v>682</v>
       </c>
     </row>
   </sheetData>
@@ -3495,39 +3790,39 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="37.26953125" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.36328125" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" customWidth="1"/>
+    <col min="1" max="1" width="37.265625" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" customWidth="1"/>
+    <col min="3" max="3" width="18.3984375" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" customWidth="1"/>
+    <col min="5" max="5" width="17.86328125" customWidth="1"/>
+    <col min="6" max="6" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="B2" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -3536,7 +3831,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3547,16 +3842,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="1" max="1" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" customWidth="1"/>
+    <col min="3" max="3" width="16.3984375" customWidth="1"/>
+    <col min="4" max="4" width="14.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -3567,7 +3862,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3575,10 +3870,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -3586,10 +3881,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -3597,10 +3892,10 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -3608,10 +3903,10 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -3619,10 +3914,10 @@
         <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -3630,10 +3925,10 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -3641,10 +3936,10 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -3652,10 +3947,10 @@
         <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -3663,10 +3958,10 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -3674,10 +3969,10 @@
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -3685,10 +3980,10 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -3696,10 +3991,10 @@
         <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -3707,10 +4002,10 @@
         <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -3718,7 +4013,29 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>201</v>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>582</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="C16" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>583</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="C17" t="s">
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -3730,38 +4047,38 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" customWidth="1"/>
-    <col min="3" max="4" width="13.36328125" customWidth="1"/>
-    <col min="5" max="5" width="19.36328125" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" customWidth="1"/>
+    <col min="2" max="2" width="30.1328125" customWidth="1"/>
+    <col min="3" max="4" width="13.3984375" customWidth="1"/>
+    <col min="5" max="5" width="19.3984375" customWidth="1"/>
+    <col min="6" max="6" width="14.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -3773,12 +4090,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -3790,12 +4107,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -3804,15 +4121,15 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -3821,15 +4138,15 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -3838,32 +4155,32 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B7" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C7" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -3872,15 +4189,15 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -3889,15 +4206,15 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -3909,12 +4226,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -3926,12 +4243,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -3943,12 +4260,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -3960,12 +4277,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B14" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -3974,15 +4291,15 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="10" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B15" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -3991,7 +4308,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -4003,14 +4320,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="1" max="1" width="13.3984375" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" customWidth="1"/>
+    <col min="3" max="3" width="19.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4021,7 +4338,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -4029,10 +4346,10 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -4045,38 +4362,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.81640625" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" customWidth="1"/>
-    <col min="4" max="4" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.86328125" customWidth="1"/>
+    <col min="3" max="3" width="12.86328125" customWidth="1"/>
+    <col min="4" max="4" width="8.73046875" customWidth="1"/>
+    <col min="5" max="5" width="19.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B2" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -4085,15 +4402,15 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B3" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -4102,15 +4419,15 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -4119,15 +4436,15 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -4136,15 +4453,15 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -4156,12 +4473,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -4170,15 +4487,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -4187,15 +4504,15 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -4204,15 +4521,15 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -4221,16 +4538,16 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -4239,15 +4556,15 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B12" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -4256,15 +4573,15 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -4273,15 +4590,15 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B14" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -4290,15 +4607,15 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C15" t="s">
         <v>62</v>
@@ -4307,15 +4624,15 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C16" t="s">
         <v>62</v>
@@ -4324,15 +4641,15 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B17" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C17" t="s">
         <v>55</v>
@@ -4341,7 +4658,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -4355,20 +4672,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="20.86328125" customWidth="1"/>
+    <col min="4" max="4" width="13.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>2</v>
@@ -4377,21 +4694,21 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -4399,18 +4716,18 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C4" t="s">
         <v>36</v>
@@ -4419,21 +4736,21 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -4441,13 +4758,13 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D6" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -4455,27 +4772,27 @@
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>87</v>
       </c>
       <c r="B8" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C8" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -4483,45 +4800,81 @@
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C11" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>588</v>
+      </c>
+      <c r="B12" t="s">
+        <v>588</v>
+      </c>
+      <c r="C12" t="s">
+        <v>589</v>
+      </c>
+      <c r="D12" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" s="13" t="s">
+        <v>594</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>594</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>595</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>596</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4531,38 +4884,38 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="36.08984375" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="13.36328125" customWidth="1"/>
-    <col min="5" max="5" width="13.81640625" customWidth="1"/>
+    <col min="2" max="2" width="36.1328125" customWidth="1"/>
+    <col min="3" max="3" width="20.86328125" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -4571,15 +4924,15 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -4588,15 +4941,15 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -4605,15 +4958,15 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -4622,15 +4975,15 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -4639,15 +4992,15 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -4656,15 +5009,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -4673,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -4683,18 +5036,18 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C57"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C95"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" customWidth="1"/>
-    <col min="2" max="2" width="12.6328125" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" customWidth="1"/>
+    <col min="1" max="1" width="16.59765625" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" customWidth="1"/>
+    <col min="3" max="3" width="18.59765625" customWidth="1"/>
+    <col min="4" max="4" width="9.86328125" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" customWidth="1"/>
+    <col min="6" max="6" width="8.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4705,194 +5058,194 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>163</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>118</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>93</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>89</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C6" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C7" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>140</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>146</v>
       </c>
       <c r="B9" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C9" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>133</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>162</v>
       </c>
       <c r="B12" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C12" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>170</v>
       </c>
       <c r="B13" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>142</v>
       </c>
       <c r="B15" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>121</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C16" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>135</v>
       </c>
       <c r="B17" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C17" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>99</v>
       </c>
       <c r="B18" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -4903,422 +5256,840 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>166</v>
       </c>
       <c r="B20" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C20" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C21" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="10" t="s">
         <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C23" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>164</v>
       </c>
       <c r="B24" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C24" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C26" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" s="10" t="s">
         <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C27" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C28" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>147</v>
       </c>
       <c r="B29" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C29" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C31" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>120</v>
       </c>
       <c r="B32" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C32" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>126</v>
       </c>
       <c r="B33" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C33" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
         <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C34" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C35" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>127</v>
       </c>
       <c r="B36" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C36" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>107</v>
       </c>
       <c r="B37" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C37" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>128</v>
       </c>
       <c r="B38" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C38" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>138</v>
       </c>
       <c r="B39" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C39" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>136</v>
       </c>
       <c r="B40" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C40" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C41" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>130</v>
       </c>
       <c r="B42" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C42" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>109</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>110</v>
       </c>
       <c r="B44" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C44" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>131</v>
       </c>
       <c r="B45" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C45" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C46" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>143</v>
       </c>
       <c r="B47" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C47" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C48" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>144</v>
       </c>
       <c r="B49" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C50" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>158</v>
       </c>
       <c r="B51" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C51" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>156</v>
       </c>
       <c r="B53" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>150</v>
       </c>
       <c r="B54" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C54" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>149</v>
       </c>
       <c r="B55" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C55" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>159</v>
       </c>
       <c r="B56" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C56" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>148</v>
       </c>
       <c r="B57" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C57" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>597</v>
+      </c>
+      <c r="B58" t="s">
+        <v>598</v>
+      </c>
+      <c r="C58" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>600</v>
+      </c>
+      <c r="B59" t="s">
+        <v>610</v>
+      </c>
+      <c r="C59" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>601</v>
+      </c>
+      <c r="B60" t="s">
+        <v>611</v>
+      </c>
+      <c r="C60" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>602</v>
+      </c>
+      <c r="B61" t="s">
+        <v>612</v>
+      </c>
+      <c r="C61" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>603</v>
+      </c>
+      <c r="B62" t="s">
+        <v>614</v>
+      </c>
+      <c r="C62" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>604</v>
+      </c>
+      <c r="B63" t="s">
+        <v>616</v>
+      </c>
+      <c r="C63" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>605</v>
+      </c>
+      <c r="B64" t="s">
+        <v>617</v>
+      </c>
+      <c r="C64" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>606</v>
+      </c>
+      <c r="B65" t="s">
+        <v>618</v>
+      </c>
+      <c r="C65" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>607</v>
+      </c>
+      <c r="B66" t="s">
+        <v>619</v>
+      </c>
+      <c r="C66" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>608</v>
+      </c>
+      <c r="B67" t="s">
+        <v>620</v>
+      </c>
+      <c r="C67" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>609</v>
+      </c>
+      <c r="B68" t="s">
+        <v>615</v>
+      </c>
+      <c r="C68" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>173</v>
+      </c>
+      <c r="B69" t="s">
+        <v>255</v>
+      </c>
+      <c r="C69" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>622</v>
+      </c>
+      <c r="B70" t="s">
+        <v>648</v>
+      </c>
+      <c r="C70" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>623</v>
+      </c>
+      <c r="B71" t="s">
+        <v>656</v>
+      </c>
+      <c r="C71" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>624</v>
+      </c>
+      <c r="B72" t="s">
+        <v>649</v>
+      </c>
+      <c r="C72" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>625</v>
+      </c>
+      <c r="B73" t="s">
+        <v>650</v>
+      </c>
+      <c r="C73" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>626</v>
+      </c>
+      <c r="B74" t="s">
+        <v>651</v>
+      </c>
+      <c r="C74" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>627</v>
+      </c>
+      <c r="B75" t="s">
+        <v>657</v>
+      </c>
+      <c r="C75" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>628</v>
+      </c>
+      <c r="B76" t="s">
+        <v>660</v>
+      </c>
+      <c r="C76" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>629</v>
+      </c>
+      <c r="B77" t="s">
+        <v>661</v>
+      </c>
+      <c r="C77" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>630</v>
+      </c>
+      <c r="B78" t="s">
+        <v>652</v>
+      </c>
+      <c r="C78" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>631</v>
+      </c>
+      <c r="B79" t="s">
+        <v>662</v>
+      </c>
+      <c r="C79" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>632</v>
+      </c>
+      <c r="B80" t="s">
+        <v>663</v>
+      </c>
+      <c r="C80" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>633</v>
+      </c>
+      <c r="B81" t="s">
+        <v>613</v>
+      </c>
+      <c r="C81" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>634</v>
+      </c>
+      <c r="B82" t="s">
+        <v>664</v>
+      </c>
+      <c r="C82" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>635</v>
+      </c>
+      <c r="B83" t="s">
+        <v>653</v>
+      </c>
+      <c r="C83" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>636</v>
+      </c>
+      <c r="B84" t="s">
+        <v>665</v>
+      </c>
+      <c r="C84" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>637</v>
+      </c>
+      <c r="B85" t="s">
+        <v>666</v>
+      </c>
+      <c r="C85" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>638</v>
+      </c>
+      <c r="B86" t="s">
+        <v>654</v>
+      </c>
+      <c r="C86" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>639</v>
+      </c>
+      <c r="B87" t="s">
+        <v>658</v>
+      </c>
+      <c r="C87" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>640</v>
+      </c>
+      <c r="B88" t="s">
+        <v>667</v>
+      </c>
+      <c r="C88" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>641</v>
+      </c>
+      <c r="B89" t="s">
+        <v>659</v>
+      </c>
+      <c r="C89" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>642</v>
+      </c>
+      <c r="B90" t="s">
+        <v>655</v>
+      </c>
+      <c r="C90" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>643</v>
+      </c>
+      <c r="B91" t="s">
+        <v>668</v>
+      </c>
+      <c r="C91" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>644</v>
+      </c>
+      <c r="B92" t="s">
+        <v>669</v>
+      </c>
+      <c r="C92" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>645</v>
+      </c>
+      <c r="B93" t="s">
+        <v>670</v>
+      </c>
+      <c r="C93" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>646</v>
+      </c>
+      <c r="B94" t="s">
+        <v>671</v>
+      </c>
+      <c r="C94" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>647</v>
+      </c>
+      <c r="B95" t="s">
+        <v>672</v>
+      </c>
+      <c r="C95" t="s">
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -5333,41 +6104,41 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.54296875" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="4" max="4" width="13.36328125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" customWidth="1"/>
-    <col min="7" max="7" width="11.54296875" customWidth="1"/>
-    <col min="8" max="8" width="8.81640625" customWidth="1"/>
+    <col min="1" max="1" width="29.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.59765625" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" customWidth="1"/>
+    <col min="5" max="5" width="18.59765625" customWidth="1"/>
+    <col min="6" max="6" width="9.86328125" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B2" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -5376,15 +6147,15 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B3" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
@@ -5396,12 +6167,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -5413,12 +6184,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -5427,15 +6198,15 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -5444,15 +6215,15 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B7" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -5461,15 +6232,15 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B8" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -5478,15 +6249,15 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B9" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -5495,15 +6266,15 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="B10" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
@@ -5512,15 +6283,15 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="B11" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -5529,15 +6300,15 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -5546,15 +6317,15 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -5563,15 +6334,15 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
@@ -5580,15 +6351,15 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
@@ -5597,15 +6368,15 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>105</v>
       </c>
       <c r="B16" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -5614,15 +6385,15 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>108</v>
       </c>
       <c r="B17" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -5631,15 +6402,15 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
@@ -5648,15 +6419,15 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
@@ -5665,15 +6436,15 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -5682,15 +6453,15 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B21" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
@@ -5699,15 +6470,15 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B22" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
@@ -5716,7 +6487,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
